--- a/49916_Cuenca_Aguaytia/_raw_reportes_xlsx/IDConfig_64970_completo.xlsx
+++ b/49916_Cuenca_Aguaytia/_raw_reportes_xlsx/IDConfig_64970_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rc46c6c8278cf41e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rab667e228ced4aa2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,66 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     28.6345</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.0744</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.5144</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     34.9703</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,7 +324,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.4662</x:v>
+        <x:v>     37.2742</x:v>
       </x:c>
     </x:row>
     <x:row>

--- a/49916_Cuenca_Aguaytia/_raw_reportes_xlsx/IDConfig_64970_completo.xlsx
+++ b/49916_Cuenca_Aguaytia/_raw_reportes_xlsx/IDConfig_64970_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rab667e228ced4aa2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R1c0c27fa79454c68"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,681 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     75.3859</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.5311</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     45.3724</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.4825</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     37.2742</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     56.1684</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     79.4938</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    134.1282</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    205.6048</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     94.4376</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     66.9901</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     97.9791</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.4644</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     75.8162</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     28.6345</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.9384</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     28.6345</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     32.0903</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     43.6100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     61.7303</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     72.0996</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     86.0664</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     93.0497</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    104.9625</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     93.6920</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     51.9617</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     62.4253</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     81.1369</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     91.8173</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    110.3026</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     89.6645</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.1945</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.4984</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.7864</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.9384</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     34.9702</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     38.1382</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     41.8820</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     47.3538</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     54.5536</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     69.1244</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     86.8694</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     40.1541</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     49.0818</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     60.6014</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>18/08/2026</x:t>
         </x:is>
       </x:c>
